--- a/p6_deployment/data/france/missing/data_preparation/df_integrated_missing.xlsx
+++ b/p6_deployment/data/france/missing/data_preparation/df_integrated_missing.xlsx
@@ -850,12 +850,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>tAufB9M</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -877,22 +877,22 @@
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>25.27272727272727</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AF2" t="n">
-        <v>179.4545454545455</v>
+        <v>179.8888888888889</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.090909090909091</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AH2" t="n">
-        <v>70.18181818181819</v>
+        <v>71</v>
       </c>
       <c r="AI2" t="n">
-        <v>2631818.181818182</v>
+        <v>2616666.666666667</v>
       </c>
       <c r="AJ2" t="n">
-        <v>76</v>
+        <v>74.77777777777777</v>
       </c>
       <c r="AK2" t="n">
         <v>26.3</v>
@@ -913,22 +913,22 @@
         <v>73.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24.44444444444444</v>
+        <v>24.65384615384615</v>
       </c>
       <c r="AR2" t="n">
-        <v>182.6666666666667</v>
+        <v>183.0384615384615</v>
       </c>
       <c r="AS2" t="n">
         <v>1</v>
       </c>
       <c r="AT2" t="n">
-        <v>68.77777777777777</v>
+        <v>68.69230769230769</v>
       </c>
       <c r="AU2" t="n">
-        <v>2005555.555555556</v>
+        <v>1913461.538461538</v>
       </c>
       <c r="AV2" t="n">
-        <v>75.4074074074074</v>
+        <v>75.11538461538461</v>
       </c>
       <c r="AW2" t="n">
         <v>25.38461538461538</v>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>tAufB9M</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -1117,22 +1117,22 @@
         <v>73.7</v>
       </c>
       <c r="AK3" t="n">
-        <v>25.54545454545455</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>179.3636363636364</v>
+        <v>179.7777777777778</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.090909090909091</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AN3" t="n">
-        <v>69.90909090909091</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="AO3" t="n">
-        <v>2568181.818181818</v>
+        <v>2538888.888888889</v>
       </c>
       <c r="AP3" t="n">
-        <v>76.18181818181819</v>
+        <v>75</v>
       </c>
       <c r="AQ3" t="n">
         <v>24.80952380952381</v>
@@ -1153,22 +1153,22 @@
         <v>74.14285714285714</v>
       </c>
       <c r="AW3" t="n">
-        <v>23.27777777777778</v>
+        <v>23.8125</v>
       </c>
       <c r="AX3" t="n">
-        <v>185.1111111111111</v>
+        <v>186.0625</v>
       </c>
       <c r="AY3" t="n">
         <v>1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>68.38888888888889</v>
+        <v>68.625</v>
       </c>
       <c r="BA3" t="n">
-        <v>2033333.333333333</v>
+        <v>1950000</v>
       </c>
       <c r="BB3" t="n">
-        <v>75.16666666666667</v>
+        <v>74.375</v>
       </c>
       <c r="BC3" t="n">
         <v>26</v>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>tAufB9M</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>OQuqpG7</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>OQuqpG7</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>zB2j3Yv</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -1751,24 +1751,28 @@
         <v>20232024</v>
       </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
       <c r="AE6" t="n">
-        <v>26.09090909090909</v>
+        <v>25.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>186.1818181818182</v>
+        <v>187.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>71.45454545454545</v>
+        <v>71.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>2863636.363636364</v>
+        <v>3030000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>74.54545454545455</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AK6" t="n">
         <v>26.9</v>
@@ -1948,12 +1952,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>d0X3cO3</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -2174,12 +2178,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -2241,22 +2245,22 @@
         <v>79.63636363636364</v>
       </c>
       <c r="AQ8" t="n">
-        <v>25.8125</v>
+        <v>26.26666666666667</v>
       </c>
       <c r="AR8" t="n">
-        <v>177.6875</v>
+        <v>178.3333333333333</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.1875</v>
+        <v>1.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>72.625</v>
+        <v>72.86666666666666</v>
       </c>
       <c r="AU8" t="n">
-        <v>5412500</v>
+        <v>5553333.333333333</v>
       </c>
       <c r="AV8" t="n">
-        <v>77.25</v>
+        <v>76.93333333333334</v>
       </c>
       <c r="AW8" t="n">
         <v>23.15789473684211</v>
@@ -2298,25 +2302,25 @@
         <v>325</v>
       </c>
       <c r="BJ8" t="n">
-        <v>26.5</v>
+        <v>22.75</v>
       </c>
       <c r="BK8" t="n">
-        <v>178.5</v>
+        <v>176.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="BM8" t="n">
         <v>4</v>
       </c>
       <c r="BN8" t="n">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="BO8" t="n">
-        <v>33000000</v>
+        <v>31500000</v>
       </c>
       <c r="BP8" t="n">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
@@ -2400,12 +2404,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -2427,22 +2431,22 @@
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="n">
-        <v>24.9</v>
+        <v>25.22222222222222</v>
       </c>
       <c r="AF9" t="n">
-        <v>181.1</v>
+        <v>180</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AH9" t="n">
-        <v>72.7</v>
+        <v>72.88888888888889</v>
       </c>
       <c r="AI9" t="n">
-        <v>4700000</v>
+        <v>4788888.888888889</v>
       </c>
       <c r="AJ9" t="n">
-        <v>77</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="AK9" t="n">
         <v>25.6</v>
@@ -2622,12 +2626,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>AaLVdEG</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -2667,22 +2671,22 @@
         <v>78.59999999999999</v>
       </c>
       <c r="AK10" t="n">
-        <v>22.22222222222222</v>
+        <v>20.88888888888889</v>
       </c>
       <c r="AL10" t="n">
-        <v>183.4444444444445</v>
+        <v>183</v>
       </c>
       <c r="AM10" t="n">
         <v>1.111111111111111</v>
       </c>
       <c r="AN10" t="n">
-        <v>70.11111111111111</v>
+        <v>69.88888888888889</v>
       </c>
       <c r="AO10" t="n">
-        <v>3600000</v>
+        <v>3833333.333333333</v>
       </c>
       <c r="AP10" t="n">
-        <v>78.33333333333333</v>
+        <v>79.66666666666667</v>
       </c>
       <c r="AQ10" t="n">
         <v>23.73684210526316</v>
@@ -2703,22 +2707,22 @@
         <v>79.73684210526316</v>
       </c>
       <c r="AW10" t="n">
-        <v>24.6</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="AX10" t="n">
-        <v>185.1</v>
+        <v>185.6666666666667</v>
       </c>
       <c r="AY10" t="n">
         <v>1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>71.8</v>
+        <v>71.77777777777777</v>
       </c>
       <c r="BA10" t="n">
-        <v>4281000</v>
+        <v>4567777.777777778</v>
       </c>
       <c r="BB10" t="n">
-        <v>76.5</v>
+        <v>77</v>
       </c>
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
@@ -2830,12 +2834,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -2857,40 +2861,40 @@
       </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>25.27272727272727</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AF11" t="n">
-        <v>181.7272727272727</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.090909090909091</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AH11" t="n">
-        <v>69.90909090909091</v>
+        <v>70.66666666666667</v>
       </c>
       <c r="AI11" t="n">
         <v>2700000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>75.90909090909091</v>
+        <v>74.66666666666667</v>
       </c>
       <c r="AK11" t="n">
-        <v>24.88888888888889</v>
+        <v>25.375</v>
       </c>
       <c r="AL11" t="n">
-        <v>183.2222222222222</v>
+        <v>183.625</v>
       </c>
       <c r="AM11" t="n">
         <v>2</v>
       </c>
       <c r="AN11" t="n">
-        <v>78.33333333333333</v>
+        <v>77.875</v>
       </c>
       <c r="AO11" t="n">
-        <v>21033333.33333333</v>
+        <v>18225000</v>
       </c>
       <c r="AP11" t="n">
-        <v>83.22222222222223</v>
+        <v>82.75</v>
       </c>
       <c r="AQ11" t="n">
         <v>23</v>
@@ -2911,22 +2915,22 @@
         <v>75.93333333333334</v>
       </c>
       <c r="AW11" t="n">
-        <v>22.11764705882353</v>
+        <v>22.1875</v>
       </c>
       <c r="AX11" t="n">
-        <v>183.5882352941177</v>
+        <v>183.8125</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.882352941176471</v>
+        <v>1.875</v>
       </c>
       <c r="AZ11" t="n">
-        <v>75.47058823529412</v>
+        <v>75.0625</v>
       </c>
       <c r="BA11" t="n">
-        <v>23758823.52941176</v>
+        <v>22525000</v>
       </c>
       <c r="BB11" t="n">
-        <v>83.29411764705883</v>
+        <v>83.0625</v>
       </c>
       <c r="BC11" t="n">
         <v>24.5</v>
@@ -3052,12 +3056,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="Y12" t="n">
@@ -3083,22 +3087,22 @@
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>23.5</v>
+        <v>23.55555555555556</v>
       </c>
       <c r="AF12" t="n">
-        <v>181</v>
+        <v>181.8888888888889</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="AH12" t="n">
-        <v>76</v>
+        <v>75.88888888888889</v>
       </c>
       <c r="AI12" t="n">
-        <v>12270000</v>
+        <v>12022222.22222222</v>
       </c>
       <c r="AJ12" t="n">
-        <v>81.5</v>
+        <v>81.44444444444444</v>
       </c>
       <c r="AK12" t="n">
         <v>25.18181818181818</v>
@@ -3122,19 +3126,19 @@
         <v>23</v>
       </c>
       <c r="AR12" t="n">
-        <v>179.8235294117647</v>
+        <v>180.25</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.294117647058824</v>
+        <v>1.25</v>
       </c>
       <c r="AT12" t="n">
-        <v>76.29411764705883</v>
+        <v>76.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>15870588.23529412</v>
+        <v>15956250</v>
       </c>
       <c r="AV12" t="n">
-        <v>82.05882352941177</v>
+        <v>82.0625</v>
       </c>
       <c r="AW12" t="n">
         <v>27.27272727272727</v>
@@ -3278,12 +3282,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>SIFtcwD</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="Y13" t="n">
@@ -3304,24 +3308,12 @@
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="AE13" t="n">
-        <v>25.33333333333333</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>181.2222222222222</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.222222222222222</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>73.44444444444444</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>7961111.111111111</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>77.88888888888889</v>
-      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="n">
         <v>24.54545454545455</v>
       </c>
@@ -3341,22 +3333,22 @@
         <v>80.54545454545455</v>
       </c>
       <c r="AQ13" t="n">
-        <v>22.78947368421053</v>
+        <v>22.94444444444444</v>
       </c>
       <c r="AR13" t="n">
-        <v>182.5263157894737</v>
+        <v>183.0555555555555</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.052631578947368</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="AT13" t="n">
-        <v>70.73684210526316</v>
+        <v>71.05555555555556</v>
       </c>
       <c r="AU13" t="n">
-        <v>5078947.368421053</v>
+        <v>5283333.333333333</v>
       </c>
       <c r="AV13" t="n">
-        <v>77.84210526315789</v>
+        <v>78.16666666666667</v>
       </c>
       <c r="AW13" t="n">
         <v>22.61111111111111</v>
@@ -3428,7 +3420,12 @@
       <c r="B14" s="2" t="n">
         <v>45431.66666666666</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">stadium municipal
@@ -3491,12 +3488,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -3571,16 +3568,16 @@
         <v>23.57142857142857</v>
       </c>
       <c r="AX14" t="n">
-        <v>179.4285714285714</v>
+        <v>179.8571428571429</v>
       </c>
       <c r="AY14" t="n">
         <v>1.214285714285714</v>
       </c>
       <c r="AZ14" t="n">
-        <v>70.5</v>
+        <v>70.71428571428571</v>
       </c>
       <c r="BA14" t="n">
-        <v>6053571.428571428</v>
+        <v>6075000</v>
       </c>
       <c r="BB14" t="n">
         <v>75.5</v>
@@ -3709,12 +3706,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="Y15" t="n">
@@ -3736,41 +3733,29 @@
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>25.09090909090909</v>
+        <v>23.72727272727273</v>
       </c>
       <c r="AF15" t="n">
-        <v>184.3636363636364</v>
+        <v>183.6363636363636</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.545454545454545</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AH15" t="n">
-        <v>76.72727272727273</v>
+        <v>75.54545454545455</v>
       </c>
       <c r="AI15" t="n">
-        <v>13236363.63636364</v>
+        <v>13100000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>80.63636363636364</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>23.125</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>183.625</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>78.875</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>27937500</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>84.625</v>
-      </c>
+        <v>80.09090909090909</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="n">
         <v>23.75</v>
       </c>
@@ -3931,12 +3916,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>SIFtcwD</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -3952,24 +3937,28 @@
         <v>20232024</v>
       </c>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
       <c r="AE16" t="n">
-        <v>26.88888888888889</v>
+        <v>27.75</v>
       </c>
       <c r="AF16" t="n">
-        <v>180.6666666666667</v>
+        <v>181.625</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.333333333333333</v>
+        <v>1.375</v>
       </c>
       <c r="AH16" t="n">
-        <v>74.66666666666667</v>
+        <v>75.875</v>
       </c>
       <c r="AI16" t="n">
-        <v>8055555.555555556</v>
+        <v>8887500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>77.44444444444444</v>
+        <v>78.125</v>
       </c>
       <c r="AK16" t="n">
         <v>27.4</v>
@@ -3990,22 +3979,22 @@
         <v>80.40000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>22</v>
+        <v>22.73684210526316</v>
       </c>
       <c r="AR16" t="n">
-        <v>184.3913043478261</v>
+        <v>184.8947368421053</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.043478260869565</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AT16" t="n">
-        <v>68.82608695652173</v>
+        <v>70.26315789473684</v>
       </c>
       <c r="AU16" t="n">
-        <v>3802173.913043478</v>
+        <v>4410526.315789473</v>
       </c>
       <c r="AV16" t="n">
-        <v>77.21739130434783</v>
+        <v>77.68421052631579</v>
       </c>
       <c r="AW16" t="n">
         <v>23.41176470588235</v>
@@ -4149,12 +4138,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="Y17" t="n">
@@ -4353,12 +4342,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="Y18" t="n">
@@ -4373,7 +4362,11 @@
       <c r="AB18" t="n">
         <v>20232024</v>
       </c>
-      <c r="AC18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
       <c r="AD18" t="inlineStr">
         <is>
           <t>d2nnj1IE</t>
@@ -4434,22 +4427,22 @@
         <v>78.66666666666667</v>
       </c>
       <c r="AW18" t="n">
-        <v>21.68181818181818</v>
+        <v>21.63157894736842</v>
       </c>
       <c r="AX18" t="n">
-        <v>179.9545454545455</v>
+        <v>178.2105263157895</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.045454545454545</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AZ18" t="n">
-        <v>70.54545454545455</v>
+        <v>70.47368421052632</v>
       </c>
       <c r="BA18" t="n">
-        <v>3436363.636363636</v>
+        <v>3363157.894736842</v>
       </c>
       <c r="BB18" t="n">
-        <v>78.22727272727273</v>
+        <v>77.94736842105263</v>
       </c>
       <c r="BC18" t="n">
         <v>23.66666666666667</v>
@@ -4575,12 +4568,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="Y19" t="n">
@@ -4660,19 +4653,19 @@
         <v>77</v>
       </c>
       <c r="AW19" t="n">
-        <v>21.45454545454545</v>
+        <v>21.21052631578947</v>
       </c>
       <c r="AX19" t="n">
-        <v>178.7272727272727</v>
+        <v>179.6315789473684</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.363636363636364</v>
+        <v>1.263157894736842</v>
       </c>
       <c r="AZ19" t="n">
-        <v>74.22727272727273</v>
+        <v>73.78947368421052</v>
       </c>
       <c r="BA19" t="n">
-        <v>11445454.54545454</v>
+        <v>10963157.89473684</v>
       </c>
       <c r="BB19" t="n">
         <v>82</v>
@@ -4801,12 +4794,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="Y20" t="n">
@@ -4886,22 +4879,22 @@
         <v>73</v>
       </c>
       <c r="AW20" t="n">
-        <v>25.86363636363636</v>
+        <v>26.19047619047619</v>
       </c>
       <c r="AX20" t="n">
-        <v>181.3636363636364</v>
+        <v>182</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.136363636363636</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AZ20" t="n">
-        <v>73.22727272727273</v>
+        <v>73.42857142857143</v>
       </c>
       <c r="BA20" t="n">
-        <v>6161363.636363637</v>
+        <v>6297619.047619048</v>
       </c>
       <c r="BB20" t="n">
-        <v>77.90909090909091</v>
+        <v>77.71428571428571</v>
       </c>
       <c r="BC20" t="n">
         <v>24</v>
@@ -5027,12 +5020,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="Y21" t="n">
@@ -5086,22 +5079,22 @@
         <v>78.90909090909091</v>
       </c>
       <c r="AQ21" t="n">
-        <v>24</v>
+        <v>23.6875</v>
       </c>
       <c r="AR21" t="n">
-        <v>182.7647058823529</v>
+        <v>182.75</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.294117647058823</v>
+        <v>2.25</v>
       </c>
       <c r="AT21" t="n">
-        <v>79.17647058823529</v>
+        <v>78.6875</v>
       </c>
       <c r="AU21" t="n">
-        <v>37552941.17647059</v>
+        <v>35306250</v>
       </c>
       <c r="AV21" t="n">
-        <v>84.70588235294117</v>
+        <v>84.5</v>
       </c>
       <c r="AW21" t="n">
         <v>22.95833333333333</v>
@@ -5245,12 +5238,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>d0X3cO3</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="Y22" t="n">
@@ -5471,12 +5464,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>AaLVdEG</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="Y23" t="n">
@@ -5502,76 +5495,76 @@
         </is>
       </c>
       <c r="AE23" t="n">
-        <v>21.125</v>
+        <v>20.88888888888889</v>
       </c>
       <c r="AF23" t="n">
-        <v>183.625</v>
+        <v>182.7777777777778</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.125</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AH23" t="n">
-        <v>71.5</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="AI23" t="n">
-        <v>4925000</v>
+        <v>4800000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>80.375</v>
+        <v>80.77777777777777</v>
       </c>
       <c r="AK23" t="n">
-        <v>25.63636363636364</v>
+        <v>27.11111111111111</v>
       </c>
       <c r="AL23" t="n">
-        <v>181.9090909090909</v>
+        <v>182.8888888888889</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.090909090909091</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AN23" t="n">
-        <v>69.72727272727273</v>
+        <v>70.44444444444444</v>
       </c>
       <c r="AO23" t="n">
-        <v>2486363.636363636</v>
+        <v>2438888.888888889</v>
       </c>
       <c r="AP23" t="n">
-        <v>76.18181818181819</v>
+        <v>75</v>
       </c>
       <c r="AQ23" t="n">
-        <v>25.3125</v>
+        <v>25.14285714285714</v>
       </c>
       <c r="AR23" t="n">
-        <v>183.625</v>
+        <v>183.4285714285714</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.375</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="AT23" t="n">
-        <v>69.875</v>
+        <v>70.42857142857143</v>
       </c>
       <c r="AU23" t="n">
-        <v>3167187.5</v>
+        <v>3464285.714285714</v>
       </c>
       <c r="AV23" t="n">
-        <v>75.375</v>
+        <v>76.07142857142857</v>
       </c>
       <c r="AW23" t="n">
-        <v>22.94444444444444</v>
+        <v>23.4375</v>
       </c>
       <c r="AX23" t="n">
-        <v>178.3888888888889</v>
+        <v>178.5</v>
       </c>
       <c r="AY23" t="n">
         <v>1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>68.38888888888889</v>
+        <v>68.625</v>
       </c>
       <c r="BA23" t="n">
-        <v>2111111.111111111</v>
+        <v>2037500</v>
       </c>
       <c r="BB23" t="n">
-        <v>75.88888888888889</v>
+        <v>75.1875</v>
       </c>
       <c r="BC23" t="n">
         <v>27.5</v>
@@ -5697,12 +5690,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>SIFtcwD</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="Y24" t="n">
@@ -5737,59 +5730,47 @@
       <c r="AJ24" t="n">
         <v>77.27272727272727</v>
       </c>
-      <c r="AK24" t="n">
-        <v>25.33333333333333</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>181.2222222222222</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.222222222222222</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>73.44444444444444</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>7961111.111111111</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>77.88888888888889</v>
-      </c>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="n">
         <v>24.65</v>
       </c>
       <c r="AR24" t="n">
-        <v>178.65</v>
+        <v>179.55</v>
       </c>
       <c r="AS24" t="n">
         <v>1.05</v>
       </c>
       <c r="AT24" t="n">
-        <v>69.2</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AU24" t="n">
-        <v>2965000</v>
+        <v>3010000</v>
       </c>
       <c r="AV24" t="n">
         <v>73.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>23.35</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="AX24" t="n">
-        <v>184</v>
+        <v>184.5555555555555</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.15</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AZ24" t="n">
-        <v>69.5</v>
+        <v>70.22222222222223</v>
       </c>
       <c r="BA24" t="n">
-        <v>3412500</v>
+        <v>3672222.222222222</v>
       </c>
       <c r="BB24" t="n">
-        <v>76.75</v>
+        <v>77.05555555555556</v>
       </c>
       <c r="BC24" t="n">
         <v>28.5</v>
@@ -5915,12 +5896,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="Y25" t="n">
@@ -5942,40 +5923,40 @@
       </c>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="n">
-        <v>24.63636363636364</v>
+        <v>23.27272727272727</v>
       </c>
       <c r="AF25" t="n">
-        <v>185.2727272727273</v>
+        <v>184.5454545454545</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.545454545454545</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AH25" t="n">
-        <v>76.09090909090909</v>
+        <v>74.90909090909091</v>
       </c>
       <c r="AI25" t="n">
-        <v>12827272.72727273</v>
+        <v>12690909.09090909</v>
       </c>
       <c r="AJ25" t="n">
-        <v>80.72727272727273</v>
+        <v>80.18181818181819</v>
       </c>
       <c r="AK25" t="n">
-        <v>24.90909090909091</v>
+        <v>24.1</v>
       </c>
       <c r="AL25" t="n">
-        <v>185.0909090909091</v>
+        <v>186</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>71.45454545454545</v>
+        <v>71.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>2927272.727272727</v>
+        <v>3100000</v>
       </c>
       <c r="AP25" t="n">
-        <v>75.18181818181819</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AQ25" t="n">
         <v>24.25</v>
@@ -6065,12 +6046,7 @@
       <c r="B26" s="2" t="n">
         <v>45418.66666666666</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t xml:space="preserve">stade pierre mauroy
@@ -6137,12 +6113,12 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="Y26" t="n">
@@ -6200,22 +6176,22 @@
         <v>79.27272727272727</v>
       </c>
       <c r="AQ26" t="n">
-        <v>25.9375</v>
+        <v>26.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>180.4375</v>
+        <v>181.2666666666667</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.1875</v>
+        <v>1.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>73.9375</v>
+        <v>74.26666666666667</v>
       </c>
       <c r="AU26" t="n">
-        <v>7935937.5</v>
+        <v>8245000</v>
       </c>
       <c r="AV26" t="n">
-        <v>77.9375</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="AW26" t="n">
         <v>25.5</v>
@@ -6345,12 +6321,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="Y27" t="n">
@@ -6411,16 +6387,16 @@
         <v>25.66666666666667</v>
       </c>
       <c r="AR27" t="n">
-        <v>180.4285714285714</v>
+        <v>180.7142857142857</v>
       </c>
       <c r="AS27" t="n">
         <v>1.285714285714286</v>
       </c>
       <c r="AT27" t="n">
-        <v>72</v>
+        <v>72.14285714285714</v>
       </c>
       <c r="AU27" t="n">
-        <v>4697619.047619048</v>
+        <v>4711904.761904762</v>
       </c>
       <c r="AV27" t="n">
         <v>75.0952380952381</v>
@@ -6567,12 +6543,12 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="Y28" t="n">
@@ -6598,22 +6574,22 @@
         </is>
       </c>
       <c r="AE28" t="n">
-        <v>26.09090909090909</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="AF28" t="n">
-        <v>180.9090909090909</v>
+        <v>181.6666666666667</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.090909090909091</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="AH28" t="n">
-        <v>70.45454545454545</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="AI28" t="n">
-        <v>2588636.363636364</v>
+        <v>2563888.888888889</v>
       </c>
       <c r="AJ28" t="n">
-        <v>75.81818181818181</v>
+        <v>74.55555555555556</v>
       </c>
       <c r="AK28" t="n">
         <v>24.36363636363636</v>
@@ -6634,22 +6610,22 @@
         <v>80.36363636363636</v>
       </c>
       <c r="AQ28" t="n">
-        <v>23.3</v>
+        <v>23.77777777777778</v>
       </c>
       <c r="AR28" t="n">
-        <v>181.25</v>
+        <v>181.6666666666667</v>
       </c>
       <c r="AS28" t="n">
         <v>1</v>
       </c>
       <c r="AT28" t="n">
-        <v>68.75</v>
+        <v>69</v>
       </c>
       <c r="AU28" t="n">
-        <v>2218750</v>
+        <v>2165277.777777778</v>
       </c>
       <c r="AV28" t="n">
-        <v>75.45</v>
+        <v>74.77777777777777</v>
       </c>
       <c r="AW28" t="n">
         <v>22.72222222222222</v>
@@ -6793,12 +6769,12 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="Y29" t="n">
@@ -6820,22 +6796,22 @@
       </c>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="n">
-        <v>24.63636363636364</v>
+        <v>24.8</v>
       </c>
       <c r="AF29" t="n">
-        <v>180.6363636363636</v>
+        <v>181.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.636363636363636</v>
+        <v>1.6</v>
       </c>
       <c r="AH29" t="n">
-        <v>77.18181818181819</v>
+        <v>77.2</v>
       </c>
       <c r="AI29" t="n">
-        <v>15500000</v>
+        <v>15600000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>81.27272727272727</v>
+        <v>81.2</v>
       </c>
       <c r="AK29" t="n">
         <v>26.90909090909091</v>
@@ -6856,22 +6832,22 @@
         <v>73.72727272727273</v>
       </c>
       <c r="AQ29" t="n">
-        <v>22.14285714285714</v>
+        <v>22.1</v>
       </c>
       <c r="AR29" t="n">
-        <v>180.5714285714286</v>
+        <v>180.95</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.333333333333333</v>
+        <v>1.3</v>
       </c>
       <c r="AT29" t="n">
-        <v>74.71428571428571</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AU29" t="n">
-        <v>11695238.0952381</v>
+        <v>11555000</v>
       </c>
       <c r="AV29" t="n">
-        <v>81.71428571428571</v>
+        <v>81.7</v>
       </c>
       <c r="AW29" t="n">
         <v>25.05555555555556</v>
@@ -7015,12 +6991,12 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>AaLVdEG</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
       <c r="Y30" t="n">
@@ -7042,40 +7018,40 @@
         </is>
       </c>
       <c r="AE30" t="n">
-        <v>25.72727272727273</v>
+        <v>25</v>
       </c>
       <c r="AF30" t="n">
-        <v>185</v>
+        <v>185.9</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>71.36363636363636</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="AI30" t="n">
-        <v>2618181.818181818</v>
+        <v>2760000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>74.36363636363636</v>
+        <v>74.7</v>
       </c>
       <c r="AK30" t="n">
-        <v>23.1</v>
+        <v>21.9</v>
       </c>
       <c r="AL30" t="n">
-        <v>184.9</v>
+        <v>184.5</v>
       </c>
       <c r="AM30" t="n">
         <v>1.1</v>
       </c>
       <c r="AN30" t="n">
-        <v>70.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="AO30" t="n">
-        <v>4260000</v>
+        <v>4470000</v>
       </c>
       <c r="AP30" t="n">
-        <v>77.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="AQ30" t="n">
         <v>25.61904761904762</v>
@@ -7096,22 +7072,22 @@
         <v>72.38095238095238</v>
       </c>
       <c r="AW30" t="n">
-        <v>25.15384615384615</v>
+        <v>24.41666666666667</v>
       </c>
       <c r="AX30" t="n">
-        <v>180.3076923076923</v>
+        <v>179.1666666666667</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.461538461538461</v>
+        <v>1.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>70.46153846153847</v>
+        <v>71.16666666666667</v>
       </c>
       <c r="BA30" t="n">
-        <v>2798076.923076923</v>
+        <v>3166666.666666667</v>
       </c>
       <c r="BB30" t="n">
-        <v>76.38461538461539</v>
+        <v>78</v>
       </c>
       <c r="BC30" t="n">
         <v>24.25</v>
@@ -7237,12 +7213,12 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>d0X3cO3</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="Y31" t="n">
@@ -7361,25 +7337,25 @@
         <v>235</v>
       </c>
       <c r="BJ31" t="n">
-        <v>22.25</v>
+        <v>22.33333333333333</v>
       </c>
       <c r="BK31" t="n">
-        <v>179.5</v>
+        <v>175.6666666666667</v>
       </c>
       <c r="BL31" t="n">
         <v>1</v>
       </c>
       <c r="BM31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN31" t="n">
-        <v>280</v>
+        <v>209</v>
       </c>
       <c r="BO31" t="n">
-        <v>11900000</v>
+        <v>8000000</v>
       </c>
       <c r="BP31" t="n">
-        <v>310</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32">
@@ -7463,12 +7439,12 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="Y32" t="n">
@@ -7685,12 +7661,12 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>d0X3cO3</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="Y33" t="n">
@@ -7705,7 +7681,11 @@
       <c r="AB33" t="n">
         <v>20232024</v>
       </c>
-      <c r="AC33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
       <c r="AD33" t="inlineStr">
         <is>
           <t>pfDZL71o</t>
@@ -7907,12 +7887,12 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="Y34" t="n">
@@ -7988,22 +7968,22 @@
         <v>78.64705882352941</v>
       </c>
       <c r="AW34" t="n">
-        <v>22.70588235294118</v>
+        <v>22.6875</v>
       </c>
       <c r="AX34" t="n">
-        <v>182.6470588235294</v>
+        <v>183.25</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.411764705882353</v>
+        <v>1.375</v>
       </c>
       <c r="AZ34" t="n">
-        <v>74.47058823529412</v>
+        <v>74.3125</v>
       </c>
       <c r="BA34" t="n">
-        <v>10247058.82352941</v>
+        <v>9981250</v>
       </c>
       <c r="BB34" t="n">
-        <v>81.05882352941177</v>
+        <v>81</v>
       </c>
       <c r="BC34" t="n">
         <v>30</v>
@@ -8129,12 +8109,12 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="Y35" t="n">
@@ -8337,12 +8317,12 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>K6b7RoB</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="Y36" t="n">
@@ -8378,22 +8358,22 @@
         <v>74.09090909090909</v>
       </c>
       <c r="AK36" t="n">
-        <v>24.6</v>
+        <v>26</v>
       </c>
       <c r="AL36" t="n">
-        <v>181.7</v>
+        <v>182.375</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN36" t="n">
-        <v>72</v>
+        <v>74.25</v>
       </c>
       <c r="AO36" t="n">
-        <v>6902500</v>
+        <v>8359375</v>
       </c>
       <c r="AP36" t="n">
-        <v>77.8</v>
+        <v>78.75</v>
       </c>
       <c r="AQ36" t="n">
         <v>23.28571428571428</v>
@@ -8414,22 +8394,22 @@
         <v>75.14285714285714</v>
       </c>
       <c r="AW36" t="n">
-        <v>22.47826086956522</v>
+        <v>22.80952380952381</v>
       </c>
       <c r="AX36" t="n">
-        <v>182.8260869565217</v>
+        <v>183.1904761904762</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.08695652173913</v>
+        <v>1.095238095238095</v>
       </c>
       <c r="AZ36" t="n">
-        <v>69.21739130434783</v>
+        <v>69.80952380952381</v>
       </c>
       <c r="BA36" t="n">
-        <v>4214130.434782608</v>
+        <v>4513095.238095238</v>
       </c>
       <c r="BB36" t="n">
-        <v>77.52173913043478</v>
+        <v>77.85714285714286</v>
       </c>
       <c r="BC36" t="n">
         <v>25</v>
@@ -8555,12 +8535,12 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="Y37" t="n">
@@ -8618,22 +8598,22 @@
         <v>79</v>
       </c>
       <c r="AQ37" t="n">
-        <v>24.52631578947368</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="AR37" t="n">
-        <v>182.4736842105263</v>
+        <v>182</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.368421052631579</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="AT37" t="n">
-        <v>71.21052631578948</v>
+        <v>71.22222222222223</v>
       </c>
       <c r="AU37" t="n">
-        <v>2857894.736842105</v>
+        <v>2800000</v>
       </c>
       <c r="AV37" t="n">
-        <v>75.57894736842105</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="AW37" t="n">
         <v>23.60869565217391</v>
@@ -8777,12 +8757,12 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>AaLVdEG</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="Y38" t="n">
@@ -8808,58 +8788,58 @@
         </is>
       </c>
       <c r="AE38" t="n">
-        <v>23</v>
+        <v>21.8</v>
       </c>
       <c r="AF38" t="n">
-        <v>184.7</v>
+        <v>184.3</v>
       </c>
       <c r="AG38" t="n">
         <v>1.1</v>
       </c>
       <c r="AH38" t="n">
-        <v>72</v>
+        <v>71.8</v>
       </c>
       <c r="AI38" t="n">
-        <v>4730000</v>
+        <v>4940000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>78.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AK38" t="n">
-        <v>24.45454545454545</v>
+        <v>23.09090909090909</v>
       </c>
       <c r="AL38" t="n">
-        <v>184.4545454545455</v>
+        <v>183.7272727272727</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.363636363636364</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AN38" t="n">
-        <v>76.45454545454545</v>
+        <v>75.27272727272727</v>
       </c>
       <c r="AO38" t="n">
-        <v>12818181.81818182</v>
+        <v>12681818.18181818</v>
       </c>
       <c r="AP38" t="n">
-        <v>81</v>
+        <v>80.45454545454545</v>
       </c>
       <c r="AQ38" t="n">
-        <v>24.66666666666667</v>
+        <v>24.38461538461538</v>
       </c>
       <c r="AR38" t="n">
-        <v>181.7333333333333</v>
+        <v>181.2307692307692</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.4</v>
+        <v>1.461538461538461</v>
       </c>
       <c r="AT38" t="n">
-        <v>69.59999999999999</v>
+        <v>70.15384615384616</v>
       </c>
       <c r="AU38" t="n">
-        <v>2998333.333333333</v>
+        <v>3292307.692307692</v>
       </c>
       <c r="AV38" t="n">
-        <v>76.06666666666666</v>
+        <v>76.92307692307692</v>
       </c>
       <c r="AW38" t="n">
         <v>24.5</v>
@@ -9003,12 +8983,12 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="Y39" t="n">
@@ -9034,22 +9014,22 @@
         </is>
       </c>
       <c r="AE39" t="n">
-        <v>25.90909090909091</v>
+        <v>26.6</v>
       </c>
       <c r="AF39" t="n">
-        <v>182.8181818181818</v>
+        <v>182.9</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.090909090909091</v>
+        <v>1.1</v>
       </c>
       <c r="AH39" t="n">
-        <v>69.45454545454545</v>
+        <v>70.2</v>
       </c>
       <c r="AI39" t="n">
-        <v>2295454.545454545</v>
+        <v>2425000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>75.36363636363636</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AK39" t="n">
         <v>24.9</v>
@@ -9070,40 +9050,40 @@
         <v>80.90000000000001</v>
       </c>
       <c r="AQ39" t="n">
-        <v>22.65217391304348</v>
+        <v>23.42105263157895</v>
       </c>
       <c r="AR39" t="n">
-        <v>178.4782608695652</v>
+        <v>179.1578947368421</v>
       </c>
       <c r="AS39" t="n">
         <v>1</v>
       </c>
       <c r="AT39" t="n">
-        <v>68.78260869565217</v>
+        <v>68.78947368421052</v>
       </c>
       <c r="AU39" t="n">
-        <v>2330434.782608696</v>
+        <v>2073684.210526316</v>
       </c>
       <c r="AV39" t="n">
-        <v>76.1304347826087</v>
+        <v>74.84210526315789</v>
       </c>
       <c r="AW39" t="n">
-        <v>23.1875</v>
+        <v>24.15384615384615</v>
       </c>
       <c r="AX39" t="n">
-        <v>178.8125</v>
+        <v>181.3076923076923</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.0625</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="AZ39" t="n">
-        <v>71.75</v>
+        <v>72.38461538461539</v>
       </c>
       <c r="BA39" t="n">
-        <v>5198437.5</v>
+        <v>5636538.461538462</v>
       </c>
       <c r="BB39" t="n">
-        <v>79.3125</v>
+        <v>78.69230769230769</v>
       </c>
       <c r="BC39" t="n">
         <v>26.33333333333333</v>
@@ -9229,12 +9209,12 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="Y40" t="n">
@@ -9252,76 +9232,76 @@
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="n">
-        <v>25.09090909090909</v>
+        <v>24.7</v>
       </c>
       <c r="AF40" t="n">
-        <v>182.5454545454545</v>
+        <v>181.9</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.272727272727273</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>81.27272727272727</v>
+        <v>81.3</v>
       </c>
       <c r="AI40" t="n">
-        <v>36000000</v>
+        <v>35450000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>85.09090909090909</v>
+        <v>85.3</v>
       </c>
       <c r="AK40" t="n">
-        <v>26.72727272727273</v>
+        <v>26.1</v>
       </c>
       <c r="AL40" t="n">
-        <v>185.0909090909091</v>
+        <v>186</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AN40" t="n">
-        <v>71.54545454545455</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AO40" t="n">
-        <v>2536363.636363636</v>
+        <v>2670000</v>
       </c>
       <c r="AP40" t="n">
-        <v>73.90909090909091</v>
+        <v>74.2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>23.77777777777778</v>
+        <v>23.47058823529412</v>
       </c>
       <c r="AR40" t="n">
-        <v>183.8333333333333</v>
+        <v>183.8823529411765</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.555555555555555</v>
+        <v>2.529411764705882</v>
       </c>
       <c r="AT40" t="n">
-        <v>79.88888888888889</v>
+        <v>79.47058823529412</v>
       </c>
       <c r="AU40" t="n">
-        <v>54827777.77777778</v>
+        <v>53729411.76470588</v>
       </c>
       <c r="AV40" t="n">
-        <v>85.44444444444444</v>
+        <v>85.29411764705883</v>
       </c>
       <c r="AW40" t="n">
-        <v>25.28571428571428</v>
+        <v>24.9</v>
       </c>
       <c r="AX40" t="n">
-        <v>182.047619047619</v>
+        <v>182.35</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.095238095238095</v>
+        <v>1</v>
       </c>
       <c r="AZ40" t="n">
-        <v>70.0952380952381</v>
+        <v>70.05</v>
       </c>
       <c r="BA40" t="n">
-        <v>2776190.476190476</v>
+        <v>2855000</v>
       </c>
       <c r="BB40" t="n">
-        <v>74.23809523809524</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="BC40" t="n">
         <v>28</v>
@@ -9447,12 +9427,12 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="Y41" t="n">
@@ -9673,12 +9653,12 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="Y42" t="n">
@@ -9693,7 +9673,11 @@
       <c r="AB42" t="n">
         <v>20232024</v>
       </c>
-      <c r="AC42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
       <c r="AD42" t="inlineStr">
         <is>
           <t>2PIvr8o4</t>
@@ -9718,22 +9702,22 @@
         <v>79.18181818181819</v>
       </c>
       <c r="AK42" t="n">
-        <v>24.63636363636364</v>
+        <v>23.27272727272727</v>
       </c>
       <c r="AL42" t="n">
-        <v>185.2727272727273</v>
+        <v>184.5454545454545</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.545454545454545</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AN42" t="n">
-        <v>76.09090909090909</v>
+        <v>74.90909090909091</v>
       </c>
       <c r="AO42" t="n">
-        <v>12827272.72727273</v>
+        <v>12690909.09090909</v>
       </c>
       <c r="AP42" t="n">
-        <v>80.72727272727273</v>
+        <v>80.18181818181819</v>
       </c>
       <c r="AQ42" t="n">
         <v>24.78947368421053</v>
@@ -9895,12 +9879,12 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="Y43" t="n">
@@ -9962,40 +9946,40 @@
         <v>81.72727272727273</v>
       </c>
       <c r="AQ43" t="n">
-        <v>23.33333333333333</v>
+        <v>23.41666666666667</v>
       </c>
       <c r="AR43" t="n">
-        <v>180.4666666666667</v>
+        <v>182.3333333333333</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AT43" t="n">
-        <v>75.53333333333333</v>
+        <v>75.16666666666667</v>
       </c>
       <c r="AU43" t="n">
-        <v>12266666.66666667</v>
+        <v>11708333.33333333</v>
       </c>
       <c r="AV43" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="AW43" t="n">
-        <v>26.85714285714286</v>
+        <v>27.46153846153846</v>
       </c>
       <c r="AX43" t="n">
-        <v>178</v>
+        <v>178.7692307692308</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.428571428571429</v>
+        <v>1.461538461538461</v>
       </c>
       <c r="AZ43" t="n">
-        <v>75.42857142857143</v>
+        <v>75.92307692307692</v>
       </c>
       <c r="BA43" t="n">
-        <v>9732142.857142856</v>
+        <v>10226923.07692308</v>
       </c>
       <c r="BB43" t="n">
-        <v>78.78571428571429</v>
+        <v>78.53846153846153</v>
       </c>
       <c r="BC43" t="n">
         <v>22.5</v>
@@ -10121,12 +10105,12 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="Y44" t="n">
@@ -10165,24 +10149,12 @@
       <c r="AJ44" t="n">
         <v>77.66666666666667</v>
       </c>
-      <c r="AK44" t="n">
-        <v>24.25</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>185</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>82</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>60725000</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>86</v>
-      </c>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
       <c r="AQ44" t="n">
         <v>23.7</v>
       </c>
@@ -10202,22 +10174,22 @@
         <v>76.45</v>
       </c>
       <c r="AW44" t="n">
-        <v>23.5</v>
+        <v>23.61904761904762</v>
       </c>
       <c r="AX44" t="n">
-        <v>182.7272727272727</v>
+        <v>182.8571428571429</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.954545454545455</v>
+        <v>1.952380952380952</v>
       </c>
       <c r="AZ44" t="n">
-        <v>77.13636363636364</v>
+        <v>76.9047619047619</v>
       </c>
       <c r="BA44" t="n">
-        <v>22945454.54545455</v>
+        <v>21966666.66666667</v>
       </c>
       <c r="BB44" t="n">
-        <v>82.86363636363636</v>
+        <v>82.66666666666667</v>
       </c>
       <c r="BC44" t="n">
         <v>26</v>
@@ -10343,12 +10315,12 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="Y45" t="n">
@@ -10366,22 +10338,22 @@
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="n">
-        <v>23.8</v>
+        <v>23.22222222222222</v>
       </c>
       <c r="AF45" t="n">
-        <v>184.1</v>
+        <v>183.5555555555555</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.2</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="AH45" t="n">
-        <v>81.2</v>
+        <v>81.22222222222223</v>
       </c>
       <c r="AI45" t="n">
-        <v>39700000</v>
+        <v>39500000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>85.59999999999999</v>
+        <v>85.88888888888889</v>
       </c>
       <c r="AK45" t="n">
         <v>26.9</v>
@@ -10402,22 +10374,22 @@
         <v>78.90000000000001</v>
       </c>
       <c r="AQ45" t="n">
-        <v>24.55</v>
+        <v>24.31578947368421</v>
       </c>
       <c r="AR45" t="n">
-        <v>183.8</v>
+        <v>183.8421052631579</v>
       </c>
       <c r="AS45" t="n">
-        <v>2.25</v>
+        <v>2.210526315789474</v>
       </c>
       <c r="AT45" t="n">
-        <v>78.84999999999999</v>
+        <v>78.42105263157895</v>
       </c>
       <c r="AU45" t="n">
-        <v>34345000</v>
+        <v>32284210.52631579</v>
       </c>
       <c r="AV45" t="n">
-        <v>83.59999999999999</v>
+        <v>83.36842105263158</v>
       </c>
       <c r="AW45" t="n">
         <v>26.45</v>
@@ -10561,12 +10533,12 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
       <c r="Y46" t="n">
@@ -10582,7 +10554,11 @@
         <v>20232024</v>
       </c>
       <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>lhUkVMh2</t>
+        </is>
+      </c>
       <c r="AE46" t="n">
         <v>23.27272727272727</v>
       </c>
@@ -10779,12 +10755,12 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>CWxpUrt</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="Y47" t="n">
@@ -10845,37 +10821,37 @@
         <v>24.66666666666667</v>
       </c>
       <c r="AR47" t="n">
-        <v>179.6666666666667</v>
+        <v>180.5238095238095</v>
       </c>
       <c r="AS47" t="n">
         <v>1.142857142857143</v>
       </c>
       <c r="AT47" t="n">
-        <v>71.04761904761905</v>
+        <v>71.47619047619048</v>
       </c>
       <c r="AU47" t="n">
-        <v>4519047.619047619</v>
+        <v>4561904.761904762</v>
       </c>
       <c r="AV47" t="n">
         <v>74.9047619047619</v>
       </c>
       <c r="AW47" t="n">
-        <v>23.65</v>
+        <v>23.76470588235294</v>
       </c>
       <c r="AX47" t="n">
-        <v>178.7</v>
+        <v>179.7058823529412</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.65</v>
+        <v>1.588235294117647</v>
       </c>
       <c r="AZ47" t="n">
-        <v>75.8</v>
+        <v>75.58823529411765</v>
       </c>
       <c r="BA47" t="n">
-        <v>12875000</v>
+        <v>12588235.29411765</v>
       </c>
       <c r="BB47" t="n">
-        <v>81.75</v>
+        <v>81.70588235294117</v>
       </c>
       <c r="BC47" t="n">
         <v>26.5</v>
@@ -11001,12 +10977,12 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>KYsw3uK</t>
+          <t>KYsw3uKl</t>
         </is>
       </c>
       <c r="Y48" t="n">
@@ -11046,22 +11022,22 @@
         <v>75.18181818181819</v>
       </c>
       <c r="AK48" t="n">
-        <v>25.90909090909091</v>
+        <v>26.6</v>
       </c>
       <c r="AL48" t="n">
-        <v>182.8181818181818</v>
+        <v>182.9</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.090909090909091</v>
+        <v>1.1</v>
       </c>
       <c r="AN48" t="n">
-        <v>69.45454545454545</v>
+        <v>70.2</v>
       </c>
       <c r="AO48" t="n">
-        <v>2295454.545454545</v>
+        <v>2425000</v>
       </c>
       <c r="AP48" t="n">
-        <v>75.36363636363636</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AQ48" t="n">
         <v>24.41666666666667</v>
@@ -11082,22 +11058,22 @@
         <v>73.875</v>
       </c>
       <c r="AW48" t="n">
-        <v>24.08333333333333</v>
+        <v>25.1</v>
       </c>
       <c r="AX48" t="n">
-        <v>178</v>
+        <v>178.1</v>
       </c>
       <c r="AY48" t="n">
         <v>1</v>
       </c>
       <c r="AZ48" t="n">
-        <v>69.75</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="BA48" t="n">
-        <v>2325000</v>
+        <v>2250000</v>
       </c>
       <c r="BB48" t="n">
-        <v>74.75</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="BC48" t="n">
         <v>19</v>
@@ -11223,12 +11199,12 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>KAwSWno</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>AaLVdEG</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
       <c r="Y49" t="n">
@@ -11272,58 +11248,58 @@
         <v>81.2</v>
       </c>
       <c r="AK49" t="n">
-        <v>24.4</v>
+        <v>23.2</v>
       </c>
       <c r="AL49" t="n">
-        <v>183</v>
+        <v>182.6</v>
       </c>
       <c r="AM49" t="n">
         <v>1.3</v>
       </c>
       <c r="AN49" t="n">
-        <v>72.2</v>
+        <v>72</v>
       </c>
       <c r="AO49" t="n">
-        <v>4340000</v>
+        <v>4550000</v>
       </c>
       <c r="AP49" t="n">
-        <v>77.8</v>
+        <v>79</v>
       </c>
       <c r="AQ49" t="n">
-        <v>24.05</v>
+        <v>24.31578947368421</v>
       </c>
       <c r="AR49" t="n">
-        <v>180.7</v>
+        <v>181.3684210526316</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.15</v>
+        <v>1.157894736842105</v>
       </c>
       <c r="AT49" t="n">
-        <v>74.05</v>
+        <v>74.31578947368421</v>
       </c>
       <c r="AU49" t="n">
-        <v>9432500</v>
+        <v>9755263.157894736</v>
       </c>
       <c r="AV49" t="n">
-        <v>79.34999999999999</v>
+        <v>79.21052631578948</v>
       </c>
       <c r="AW49" t="n">
-        <v>22.27777777777778</v>
+        <v>22.29411764705882</v>
       </c>
       <c r="AX49" t="n">
-        <v>183.7222222222222</v>
+        <v>183.3529411764706</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.166666666666667</v>
+        <v>1.176470588235294</v>
       </c>
       <c r="AZ49" t="n">
-        <v>69.5</v>
+        <v>70.05882352941177</v>
       </c>
       <c r="BA49" t="n">
-        <v>3593055.555555556</v>
+        <v>3776470.588235294</v>
       </c>
       <c r="BB49" t="n">
-        <v>77.33333333333333</v>
+        <v>77.82352941176471</v>
       </c>
       <c r="BC49" t="n">
         <v>23.6</v>
@@ -11449,12 +11425,12 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>K6b7RoB</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="Y50" t="n">
@@ -11476,22 +11452,22 @@
         </is>
       </c>
       <c r="AE50" t="n">
-        <v>24.1</v>
+        <v>24.55555555555556</v>
       </c>
       <c r="AF50" t="n">
-        <v>182.3</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.2</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="AH50" t="n">
-        <v>72.90000000000001</v>
+        <v>73.77777777777777</v>
       </c>
       <c r="AI50" t="n">
-        <v>6787500</v>
+        <v>7386111.111111111</v>
       </c>
       <c r="AJ50" t="n">
-        <v>78.7</v>
+        <v>79.44444444444444</v>
       </c>
       <c r="AK50" t="n">
         <v>25.36363636363636</v>
@@ -11512,22 +11488,22 @@
         <v>77.63636363636364</v>
       </c>
       <c r="AQ50" t="n">
-        <v>23.95454545454545</v>
+        <v>24.14285714285714</v>
       </c>
       <c r="AR50" t="n">
-        <v>181.8636363636364</v>
+        <v>182.2857142857143</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.136363636363636</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AT50" t="n">
-        <v>69.72727272727273</v>
+        <v>69.95238095238095</v>
       </c>
       <c r="AU50" t="n">
-        <v>4521590.909090909</v>
+        <v>4670238.095238095</v>
       </c>
       <c r="AV50" t="n">
-        <v>76.68181818181819</v>
+        <v>76.9047619047619</v>
       </c>
       <c r="AW50" t="n">
         <v>24.38888888888889</v>
@@ -11548,25 +11524,25 @@
         <v>76.22222222222223</v>
       </c>
       <c r="BC50" t="n">
-        <v>21</v>
+        <v>21.75</v>
       </c>
       <c r="BD50" t="n">
-        <v>182.6</v>
+        <v>182</v>
       </c>
       <c r="BE50" t="n">
         <v>1</v>
       </c>
       <c r="BF50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BG50" t="n">
-        <v>345</v>
+        <v>284</v>
       </c>
       <c r="BH50" t="n">
-        <v>19350000</v>
+        <v>18600000</v>
       </c>
       <c r="BI50" t="n">
-        <v>392</v>
+        <v>316</v>
       </c>
       <c r="BJ50" t="n">
         <v>27.66666666666667</v>
@@ -11671,12 +11647,12 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>d0X3cO3</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="Y51" t="n">
@@ -11893,12 +11869,12 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="Y52" t="n">
@@ -12119,12 +12095,12 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>zuUcoUw</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>pYaUUJs</t>
+          <t>pYaUUJs1</t>
         </is>
       </c>
       <c r="Y53" t="n">
@@ -12150,40 +12126,40 @@
         </is>
       </c>
       <c r="AE53" t="n">
-        <v>25.09090909090909</v>
+        <v>23.72727272727273</v>
       </c>
       <c r="AF53" t="n">
-        <v>184.3636363636364</v>
+        <v>183.6363636363636</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.545454545454545</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="AH53" t="n">
-        <v>76.72727272727273</v>
+        <v>75.54545454545455</v>
       </c>
       <c r="AI53" t="n">
-        <v>13236363.63636364</v>
+        <v>13100000</v>
       </c>
       <c r="AJ53" t="n">
-        <v>80.63636363636364</v>
+        <v>80.09090909090909</v>
       </c>
       <c r="AK53" t="n">
-        <v>22.66666666666667</v>
+        <v>22.75</v>
       </c>
       <c r="AL53" t="n">
-        <v>180.4444444444445</v>
+        <v>179.125</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.111111111111111</v>
+        <v>1.125</v>
       </c>
       <c r="AN53" t="n">
         <v>71</v>
       </c>
       <c r="AO53" t="n">
-        <v>4177777.777777778</v>
+        <v>4212500</v>
       </c>
       <c r="AP53" t="n">
-        <v>78.22222222222223</v>
+        <v>78</v>
       </c>
       <c r="AQ53" t="n">
         <v>23.66666666666667</v>
@@ -12345,12 +12321,12 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>0tIbS51</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="Y54" t="n">
@@ -12425,16 +12401,16 @@
         <v>23.52380952380953</v>
       </c>
       <c r="AX54" t="n">
-        <v>180</v>
+        <v>180.2857142857143</v>
       </c>
       <c r="AY54" t="n">
         <v>1.047619047619048</v>
       </c>
       <c r="AZ54" t="n">
-        <v>70.19047619047619</v>
+        <v>70.33333333333333</v>
       </c>
       <c r="BA54" t="n">
-        <v>4500000</v>
+        <v>4514285.714285715</v>
       </c>
       <c r="BB54" t="n">
         <v>75.23809523809524</v>
@@ -12563,12 +12539,12 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>OYUbATy</t>
+          <t>OYUbATyb</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="Y55" t="n">
@@ -12785,12 +12761,12 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>25Wk0Fk</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>YTLwacK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="Y56" t="n">
@@ -12812,22 +12788,22 @@
         </is>
       </c>
       <c r="AE56" t="n">
-        <v>27</v>
+        <v>26.4</v>
       </c>
       <c r="AF56" t="n">
-        <v>184.5454545454545</v>
+        <v>185.4</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="AH56" t="n">
-        <v>71.90909090909091</v>
+        <v>72</v>
       </c>
       <c r="AI56" t="n">
-        <v>2954545.454545455</v>
+        <v>3130000</v>
       </c>
       <c r="AJ56" t="n">
-        <v>74.36363636363636</v>
+        <v>74.7</v>
       </c>
       <c r="AK56" t="n">
         <v>27.09090909090909</v>
@@ -12848,22 +12824,22 @@
         <v>74.90909090909091</v>
       </c>
       <c r="AQ56" t="n">
-        <v>23.83333333333333</v>
+        <v>23.43478260869565</v>
       </c>
       <c r="AR56" t="n">
-        <v>180.3333333333333</v>
+        <v>180.5217391304348</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.083333333333333</v>
+        <v>1</v>
       </c>
       <c r="AT56" t="n">
-        <v>68.375</v>
+        <v>68.26086956521739</v>
       </c>
       <c r="AU56" t="n">
-        <v>2116666.666666667</v>
+        <v>2156521.739130435</v>
       </c>
       <c r="AV56" t="n">
-        <v>73.58333333333333</v>
+        <v>73.69565217391305</v>
       </c>
       <c r="AW56" t="n">
         <v>24.95238095238095</v>
@@ -13007,12 +12983,12 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>UapruDa</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="Y57" t="n">
@@ -13229,12 +13205,12 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>YHU1oFV</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>8MdrBIU</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="Y58" t="n">
@@ -13270,22 +13246,22 @@
         <v>78.8</v>
       </c>
       <c r="AK58" t="n">
-        <v>23.09090909090909</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="AL58" t="n">
-        <v>183</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="AM58" t="n">
-        <v>2.272727272727273</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="AN58" t="n">
-        <v>82.27272727272727</v>
+        <v>82.44444444444444</v>
       </c>
       <c r="AO58" t="n">
-        <v>56954545.45454545</v>
+        <v>60166666.66666666</v>
       </c>
       <c r="AP58" t="n">
-        <v>86.81818181818181</v>
+        <v>87.22222222222223</v>
       </c>
       <c r="AQ58" t="n">
         <v>24.86363636363636</v>
@@ -13433,12 +13409,12 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>6FKPxxg</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>lb31RXz</t>
+          <t>lb31RXzP</t>
         </is>
       </c>
       <c r="Y59" t="n">
@@ -13623,12 +13599,12 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>OpNm82M</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>h89kUbu</t>
+          <t>h89kUbu5</t>
         </is>
       </c>
       <c r="Y60" t="n">
@@ -13700,22 +13676,22 @@
         <v>72.45454545454545</v>
       </c>
       <c r="AW60" t="n">
-        <v>25.22727272727273</v>
+        <v>25.09523809523809</v>
       </c>
       <c r="AX60" t="n">
-        <v>179.1818181818182</v>
+        <v>178.9047619047619</v>
       </c>
       <c r="AY60" t="n">
         <v>1</v>
       </c>
       <c r="AZ60" t="n">
-        <v>61.68181818181818</v>
+        <v>61.61904761904762</v>
       </c>
       <c r="BA60" t="n">
-        <v>557727.2727272727</v>
+        <v>564047.6190476191</v>
       </c>
       <c r="BB60" t="n">
-        <v>66.22727272727273</v>
+        <v>66.38095238095238</v>
       </c>
       <c r="BC60" t="inlineStr"/>
       <c r="BD60" t="inlineStr"/>
@@ -13813,12 +13789,12 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>bauuckz</t>
+          <t>bauuckzB</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>zB2j3Yv</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="Y61" t="n">
@@ -14003,12 +13979,12 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>xt8jqdt</t>
+          <t>xt8jqdte</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>fm0Qb28</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="Y62" t="n">
@@ -14044,22 +14020,22 @@
         <v>73.90000000000001</v>
       </c>
       <c r="AK62" t="n">
-        <v>24.2</v>
+        <v>24.09090909090909</v>
       </c>
       <c r="AL62" t="n">
-        <v>182.2</v>
+        <v>182.0909090909091</v>
       </c>
       <c r="AM62" t="n">
         <v>1</v>
       </c>
       <c r="AN62" t="n">
-        <v>65.3</v>
+        <v>65.54545454545455</v>
       </c>
       <c r="AO62" t="n">
-        <v>1080000</v>
+        <v>1154545.454545455</v>
       </c>
       <c r="AP62" t="n">
-        <v>70.8</v>
+        <v>71.09090909090909</v>
       </c>
       <c r="AQ62" t="n">
         <v>20.3</v>
@@ -14193,12 +14169,12 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Q9EVqFe</t>
+          <t>Q9EVqFe4</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>boLlrzT</t>
+          <t>boLlrzTH</t>
         </is>
       </c>
       <c r="Y63" t="n">
@@ -14216,76 +14192,76 @@
       <c r="AC63" t="inlineStr"/>
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="n">
-        <v>24.5</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="AF63" t="n">
-        <v>182.4</v>
+        <v>180.5555555555555</v>
       </c>
       <c r="AG63" t="n">
         <v>1</v>
       </c>
       <c r="AH63" t="n">
-        <v>67.3</v>
+        <v>66.55555555555556</v>
       </c>
       <c r="AI63" t="n">
-        <v>1522500</v>
+        <v>1602777.777777778</v>
       </c>
       <c r="AJ63" t="n">
-        <v>73.8</v>
+        <v>74.11111111111111</v>
       </c>
       <c r="AK63" t="n">
-        <v>24.36363636363636</v>
+        <v>24.3</v>
       </c>
       <c r="AL63" t="n">
-        <v>181.1818181818182</v>
+        <v>181.1</v>
       </c>
       <c r="AM63" t="n">
         <v>1</v>
       </c>
       <c r="AN63" t="n">
-        <v>64.09090909090909</v>
+        <v>63.8</v>
       </c>
       <c r="AO63" t="n">
-        <v>818181.8181818182</v>
+        <v>770000</v>
       </c>
       <c r="AP63" t="n">
-        <v>70.09090909090909</v>
+        <v>70</v>
       </c>
       <c r="AQ63" t="n">
         <v>24.10526315789474</v>
       </c>
       <c r="AR63" t="n">
-        <v>184.2105263157895</v>
+        <v>183.8947368421053</v>
       </c>
       <c r="AS63" t="n">
         <v>1</v>
       </c>
       <c r="AT63" t="n">
-        <v>65.15789473684211</v>
+        <v>65</v>
       </c>
       <c r="AU63" t="n">
-        <v>1243684.210526316</v>
+        <v>1227894.736842105</v>
       </c>
       <c r="AV63" t="n">
         <v>73.10526315789474</v>
       </c>
       <c r="AW63" t="n">
-        <v>22.0625</v>
+        <v>21.86666666666667</v>
       </c>
       <c r="AX63" t="n">
-        <v>181.8125</v>
+        <v>181.8</v>
       </c>
       <c r="AY63" t="n">
         <v>1</v>
       </c>
       <c r="AZ63" t="n">
-        <v>61.25</v>
+        <v>60.86666666666667</v>
       </c>
       <c r="BA63" t="n">
-        <v>782812.5</v>
+        <v>748333.3333333334</v>
       </c>
       <c r="BB63" t="n">
-        <v>68.8125</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="BC63" t="inlineStr"/>
       <c r="BD63" t="inlineStr"/>
@@ -14383,12 +14359,12 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>feuQknK</t>
+          <t>feuQknKS</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>dS1CBpl</t>
+          <t>dS1CBple</t>
         </is>
       </c>
       <c r="Y64" t="n">
@@ -14406,58 +14382,58 @@
       <c r="AC64" t="inlineStr"/>
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="n">
-        <v>25.81818181818182</v>
+        <v>26.1</v>
       </c>
       <c r="AF64" t="n">
-        <v>181.8181818181818</v>
+        <v>181.7</v>
       </c>
       <c r="AG64" t="n">
         <v>1</v>
       </c>
       <c r="AH64" t="n">
-        <v>67.18181818181819</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AI64" t="n">
-        <v>1345454.545454545</v>
+        <v>1380000</v>
       </c>
       <c r="AJ64" t="n">
-        <v>71.27272727272727</v>
+        <v>71.3</v>
       </c>
       <c r="AK64" t="n">
-        <v>25</v>
+        <v>25.27272727272727</v>
       </c>
       <c r="AL64" t="n">
-        <v>179.6363636363636</v>
+        <v>180.4545454545455</v>
       </c>
       <c r="AM64" t="n">
         <v>1</v>
       </c>
       <c r="AN64" t="n">
-        <v>66.36363636363636</v>
+        <v>66.72727272727273</v>
       </c>
       <c r="AO64" t="n">
-        <v>1409090.909090909</v>
+        <v>1436363.636363636</v>
       </c>
       <c r="AP64" t="n">
-        <v>71.09090909090909</v>
+        <v>71.18181818181819</v>
       </c>
       <c r="AQ64" t="n">
-        <v>26</v>
+        <v>28.66666666666667</v>
       </c>
       <c r="AR64" t="n">
-        <v>179.578947368421</v>
+        <v>180.7222222222222</v>
       </c>
       <c r="AS64" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="AT64" t="n">
-        <v>66.31578947368421</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="AU64" t="n">
-        <v>1322368.421052632</v>
+        <v>1590277.777777778</v>
       </c>
       <c r="AV64" t="n">
-        <v>71.57894736842105</v>
+        <v>72.61111111111111</v>
       </c>
       <c r="AW64" t="n">
         <v>25</v>
@@ -14573,12 +14549,12 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>4vG8dmr</t>
+          <t>4vG8dmrf</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ys1Pb7w</t>
+          <t>Ys1Pb7ws</t>
         </is>
       </c>
       <c r="Y65" t="n">
@@ -14596,58 +14572,58 @@
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="n">
-        <v>26.11111111111111</v>
+        <v>25.8</v>
       </c>
       <c r="AF65" t="n">
-        <v>181.3333333333333</v>
+        <v>180.6</v>
       </c>
       <c r="AG65" t="n">
         <v>1</v>
       </c>
       <c r="AH65" t="n">
-        <v>67</v>
+        <v>66.3</v>
       </c>
       <c r="AI65" t="n">
-        <v>1152777.777777778</v>
+        <v>1075000</v>
       </c>
       <c r="AJ65" t="n">
-        <v>69.44444444444444</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AK65" t="n">
-        <v>26.4</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="AL65" t="n">
-        <v>184.2</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="AM65" t="n">
         <v>1</v>
       </c>
       <c r="AN65" t="n">
-        <v>66.7</v>
+        <v>66.22222222222223</v>
       </c>
       <c r="AO65" t="n">
-        <v>1197500</v>
+        <v>1263888.888888889</v>
       </c>
       <c r="AP65" t="n">
-        <v>72.90000000000001</v>
+        <v>73.11111111111111</v>
       </c>
       <c r="AQ65" t="n">
-        <v>27.55</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="AR65" t="n">
-        <v>176.25</v>
+        <v>176.1428571428571</v>
       </c>
       <c r="AS65" t="n">
         <v>1</v>
       </c>
       <c r="AT65" t="n">
-        <v>65.75</v>
+        <v>65.47619047619048</v>
       </c>
       <c r="AU65" t="n">
-        <v>901250</v>
+        <v>876190.4761904762</v>
       </c>
       <c r="AV65" t="n">
-        <v>68.84999999999999</v>
+        <v>68.71428571428571</v>
       </c>
       <c r="AW65" t="n">
         <v>28.31818181818182</v>
@@ -14763,12 +14739,12 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>QuOmnHM</t>
+          <t>QuOmnHMq</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>tAufB9M</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="Y66" t="n">
@@ -14786,22 +14762,22 @@
       <c r="AC66" t="inlineStr"/>
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="n">
-        <v>26.09090909090909</v>
+        <v>26.7</v>
       </c>
       <c r="AF66" t="n">
-        <v>186.5454545454545</v>
+        <v>186.7</v>
       </c>
       <c r="AG66" t="n">
         <v>1</v>
       </c>
       <c r="AH66" t="n">
-        <v>65.90909090909091</v>
+        <v>66.2</v>
       </c>
       <c r="AI66" t="n">
-        <v>954545.4545454546</v>
+        <v>950000</v>
       </c>
       <c r="AJ66" t="n">
-        <v>69.54545454545455</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AK66" t="n">
         <v>23.8</v>
@@ -14953,12 +14929,12 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>OQuqpG7</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Cp0gM1r</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="Y67" t="n">
@@ -15141,12 +15117,12 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>bXIqj1k</t>
+          <t>bXIqj1ke</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>SIiBpBr</t>
+          <t>SIiBpBrs</t>
         </is>
       </c>
       <c r="Y68" t="n">
@@ -15182,58 +15158,58 @@
         <v>71.59999999999999</v>
       </c>
       <c r="AK68" t="n">
-        <v>26</v>
+        <v>26.11111111111111</v>
       </c>
       <c r="AL68" t="n">
-        <v>183.8888888888889</v>
+        <v>182</v>
       </c>
       <c r="AM68" t="n">
         <v>1</v>
       </c>
       <c r="AN68" t="n">
-        <v>64.66666666666667</v>
+        <v>64.22222222222223</v>
       </c>
       <c r="AO68" t="n">
-        <v>888888.8888888889</v>
+        <v>788888.8888888889</v>
       </c>
       <c r="AP68" t="n">
-        <v>68.55555555555556</v>
+        <v>68</v>
       </c>
       <c r="AQ68" t="n">
-        <v>22.8125</v>
+        <v>23.69230769230769</v>
       </c>
       <c r="AR68" t="n">
-        <v>178.6875</v>
+        <v>175.8461538461538</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.0625</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="AT68" t="n">
-        <v>63.75</v>
+        <v>63.46153846153846</v>
       </c>
       <c r="AU68" t="n">
-        <v>1092187.5</v>
+        <v>951923.0769230769</v>
       </c>
       <c r="AV68" t="n">
-        <v>72</v>
+        <v>69.92307692307692</v>
       </c>
       <c r="AW68" t="n">
-        <v>25.44444444444444</v>
+        <v>25.5</v>
       </c>
       <c r="AX68" t="n">
-        <v>182.3888888888889</v>
+        <v>181.4444444444445</v>
       </c>
       <c r="AY68" t="n">
         <v>1</v>
       </c>
       <c r="AZ68" t="n">
-        <v>63.61111111111111</v>
+        <v>63.38888888888889</v>
       </c>
       <c r="BA68" t="n">
-        <v>755555.5555555555</v>
+        <v>705555.5555555555</v>
       </c>
       <c r="BB68" t="n">
-        <v>67.44444444444444</v>
+        <v>67.16666666666667</v>
       </c>
       <c r="BC68" t="inlineStr"/>
       <c r="BD68" t="inlineStr"/>
@@ -15331,12 +15307,12 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>Cp0gM1r</t>
+          <t>Cp0gM1r4</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>feuQknK</t>
+          <t>feuQknKS</t>
         </is>
       </c>
       <c r="Y69" t="n">
@@ -15372,22 +15348,22 @@
         <v>69.81818181818181</v>
       </c>
       <c r="AK69" t="n">
-        <v>26.63636363636364</v>
+        <v>28.5</v>
       </c>
       <c r="AL69" t="n">
-        <v>181.2727272727273</v>
+        <v>181.9</v>
       </c>
       <c r="AM69" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AN69" t="n">
-        <v>67.90909090909091</v>
+        <v>69.7</v>
       </c>
       <c r="AO69" t="n">
-        <v>1413636.363636364</v>
+        <v>1605000</v>
       </c>
       <c r="AP69" t="n">
-        <v>71.09090909090909</v>
+        <v>71.7</v>
       </c>
       <c r="AQ69" t="n">
         <v>25.2</v>
@@ -15408,22 +15384,22 @@
         <v>71.8</v>
       </c>
       <c r="AW69" t="n">
-        <v>26.47368421052632</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="AX69" t="n">
-        <v>180.6842105263158</v>
+        <v>180.5555555555555</v>
       </c>
       <c r="AY69" t="n">
         <v>1</v>
       </c>
       <c r="AZ69" t="n">
-        <v>66.73684210526316</v>
+        <v>66.94444444444444</v>
       </c>
       <c r="BA69" t="n">
-        <v>1328947.368421053</v>
+        <v>1347222.222222222</v>
       </c>
       <c r="BB69" t="n">
-        <v>70.15789473684211</v>
+        <v>70.11111111111111</v>
       </c>
       <c r="BC69" t="inlineStr"/>
       <c r="BD69" t="inlineStr"/>
@@ -15521,12 +15497,12 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>dS1CBpl</t>
+          <t>dS1CBple</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>OpNm82M</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="Y70" t="n">
@@ -15544,22 +15520,22 @@
       <c r="AC70" t="inlineStr"/>
       <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="n">
-        <v>25.63636363636364</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="AF70" t="n">
-        <v>182.6363636363636</v>
+        <v>183.4545454545455</v>
       </c>
       <c r="AG70" t="n">
         <v>1</v>
       </c>
       <c r="AH70" t="n">
-        <v>67</v>
+        <v>67.36363636363636</v>
       </c>
       <c r="AI70" t="n">
-        <v>1279545.454545455</v>
+        <v>1306818.181818182</v>
       </c>
       <c r="AJ70" t="n">
-        <v>70.90909090909091</v>
+        <v>71</v>
       </c>
       <c r="AK70" t="n">
         <v>25.63636363636364</v>
@@ -15711,12 +15687,12 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>SIiBpBr</t>
+          <t>SIiBpBrs</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>6FKPxxg</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="Y71" t="n">
@@ -15901,12 +15877,12 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>h89kUbu</t>
+          <t>h89kUbu5</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>xt8jqdt</t>
+          <t>xt8jqdte</t>
         </is>
       </c>
       <c r="Y72" t="n">
@@ -16091,12 +16067,12 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>lb31RXz</t>
+          <t>lb31RXzP</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Q9EVqFe</t>
+          <t>Q9EVqFe4</t>
         </is>
       </c>
       <c r="Y73" t="n">
@@ -16132,22 +16108,22 @@
         <v>70.81818181818181</v>
       </c>
       <c r="AK73" t="n">
-        <v>24.88888888888889</v>
+        <v>23.625</v>
       </c>
       <c r="AL73" t="n">
-        <v>183.3333333333333</v>
+        <v>181.375</v>
       </c>
       <c r="AM73" t="n">
         <v>1</v>
       </c>
       <c r="AN73" t="n">
-        <v>68.11111111111111</v>
+        <v>67.375</v>
       </c>
       <c r="AO73" t="n">
-        <v>1788888.888888889</v>
+        <v>1912500</v>
       </c>
       <c r="AP73" t="n">
-        <v>74.22222222222223</v>
+        <v>74.625</v>
       </c>
       <c r="AQ73" t="n">
         <v>24.27777777777778</v>
@@ -16171,16 +16147,16 @@
         <v>26.77777777777778</v>
       </c>
       <c r="AX73" t="n">
-        <v>183.2777777777778</v>
+        <v>182.9444444444445</v>
       </c>
       <c r="AY73" t="n">
         <v>1</v>
       </c>
       <c r="AZ73" t="n">
-        <v>66.94444444444444</v>
+        <v>66.77777777777777</v>
       </c>
       <c r="BA73" t="n">
-        <v>1219722.222222222</v>
+        <v>1203055.555555556</v>
       </c>
       <c r="BB73" t="n">
         <v>71.61111111111111</v>
@@ -16281,12 +16257,12 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>Ys1Pb7w</t>
+          <t>Ys1Pb7ws</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>bXIqj1k</t>
+          <t>bXIqj1ke</t>
         </is>
       </c>
       <c r="Y74" t="n">
@@ -16304,22 +16280,22 @@
       <c r="AC74" t="inlineStr"/>
       <c r="AD74" t="inlineStr"/>
       <c r="AE74" t="n">
-        <v>27.4</v>
+        <v>26.77777777777778</v>
       </c>
       <c r="AF74" t="n">
-        <v>183.7</v>
+        <v>182.1111111111111</v>
       </c>
       <c r="AG74" t="n">
         <v>1</v>
       </c>
       <c r="AH74" t="n">
-        <v>66.90000000000001</v>
+        <v>66.44444444444444</v>
       </c>
       <c r="AI74" t="n">
-        <v>1125000</v>
+        <v>1183333.333333333</v>
       </c>
       <c r="AJ74" t="n">
-        <v>72.09999999999999</v>
+        <v>72.22222222222223</v>
       </c>
       <c r="AK74" t="n">
         <v>25.54545454545455</v>
@@ -16358,22 +16334,22 @@
         <v>70.59090909090909</v>
       </c>
       <c r="AW74" t="n">
-        <v>22.95454545454545</v>
+        <v>23.57894736842105</v>
       </c>
       <c r="AX74" t="n">
-        <v>179.9090909090909</v>
+        <v>178.1578947368421</v>
       </c>
       <c r="AY74" t="n">
-        <v>1.045454545454545</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AZ74" t="n">
-        <v>63.54545454545455</v>
+        <v>63.31578947368421</v>
       </c>
       <c r="BA74" t="n">
-        <v>1100000</v>
+        <v>1005263.157894737</v>
       </c>
       <c r="BB74" t="n">
-        <v>71.68181818181819</v>
+        <v>70.21052631578948</v>
       </c>
       <c r="BC74" t="inlineStr"/>
       <c r="BD74" t="inlineStr"/>
@@ -16471,12 +16447,12 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>zB2j3Yv</t>
+          <t>zB2j3YvM</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>4vG8dmr</t>
+          <t>4vG8dmrf</t>
         </is>
       </c>
       <c r="Y75" t="n">
@@ -16512,22 +16488,22 @@
         <v>69.90000000000001</v>
       </c>
       <c r="AK75" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="AL75" t="n">
-        <v>181</v>
+        <v>180.3</v>
       </c>
       <c r="AM75" t="n">
         <v>1</v>
       </c>
       <c r="AN75" t="n">
-        <v>66.22222222222223</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AO75" t="n">
-        <v>1147222.222222222</v>
+        <v>1070000</v>
       </c>
       <c r="AP75" t="n">
-        <v>70.22222222222223</v>
+        <v>69.8</v>
       </c>
       <c r="AQ75" t="n">
         <v>27</v>
@@ -16661,12 +16637,12 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>fm0Qb28</t>
+          <t>fm0Qb28B</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>bauuckz</t>
+          <t>bauuckzB</t>
         </is>
       </c>
       <c r="Y76" t="n">
@@ -16684,22 +16660,22 @@
       <c r="AC76" t="inlineStr"/>
       <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="n">
-        <v>27.3</v>
+        <v>26.90909090909091</v>
       </c>
       <c r="AF76" t="n">
-        <v>179.1</v>
+        <v>179.2727272727273</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.1</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="AH76" t="n">
-        <v>66.59999999999999</v>
+        <v>66.72727272727273</v>
       </c>
       <c r="AI76" t="n">
-        <v>1020000</v>
+        <v>1100000</v>
       </c>
       <c r="AJ76" t="n">
-        <v>69.09999999999999</v>
+        <v>69.54545454545455</v>
       </c>
       <c r="AK76" t="n">
         <v>26.18181818181818</v>
@@ -16851,12 +16827,12 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>tAufB9M</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>OQuqpG7</t>
+          <t>OQuqpG7i</t>
         </is>
       </c>
       <c r="Y77" t="n">
@@ -17041,12 +17017,12 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>boLlrzT</t>
+          <t>boLlrzTH</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>QuOmnHM</t>
+          <t>QuOmnHMq</t>
         </is>
       </c>
       <c r="Y78" t="n">
@@ -17082,58 +17058,58 @@
         <v>69.90909090909091</v>
       </c>
       <c r="AK78" t="n">
-        <v>25.27272727272727</v>
+        <v>25.8</v>
       </c>
       <c r="AL78" t="n">
-        <v>185.1818181818182</v>
+        <v>185.2</v>
       </c>
       <c r="AM78" t="n">
         <v>1</v>
       </c>
       <c r="AN78" t="n">
-        <v>65.90909090909091</v>
+        <v>66.2</v>
       </c>
       <c r="AO78" t="n">
-        <v>1090909.090909091</v>
+        <v>1100000</v>
       </c>
       <c r="AP78" t="n">
-        <v>70.18181818181819</v>
+        <v>69.8</v>
       </c>
       <c r="AQ78" t="n">
-        <v>22.9375</v>
+        <v>22.46153846153846</v>
       </c>
       <c r="AR78" t="n">
-        <v>181.75</v>
+        <v>181.6923076923077</v>
       </c>
       <c r="AS78" t="n">
         <v>1</v>
       </c>
       <c r="AT78" t="n">
-        <v>62.9375</v>
+        <v>62</v>
       </c>
       <c r="AU78" t="n">
-        <v>935937.5</v>
+        <v>851923.0769230769</v>
       </c>
       <c r="AV78" t="n">
-        <v>69.3125</v>
+        <v>68.92307692307692</v>
       </c>
       <c r="AW78" t="n">
-        <v>23.45454545454545</v>
+        <v>23.61904761904762</v>
       </c>
       <c r="AX78" t="n">
-        <v>182.0909090909091</v>
+        <v>181.952380952381</v>
       </c>
       <c r="AY78" t="n">
         <v>1</v>
       </c>
       <c r="AZ78" t="n">
-        <v>63.59090909090909</v>
+        <v>63.61904761904762</v>
       </c>
       <c r="BA78" t="n">
-        <v>1007954.545454545</v>
+        <v>1008333.333333333</v>
       </c>
       <c r="BB78" t="n">
-        <v>70.18181818181819</v>
+        <v>70</v>
       </c>
       <c r="BC78" t="inlineStr"/>
       <c r="BD78" t="inlineStr"/>
